--- a/data/trans_orig/P21D4_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D4_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psicólogo) en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psicólogo) en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>188804</t>
+          <t>188692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>212298</t>
+          <t>212019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190438</t>
+          <t>190066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>204934</t>
+          <t>204952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385958</t>
+          <t>386046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>412582</t>
+          <t>413660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32169</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>27098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25344</t>
+          <t>24476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51685</t>
+          <t>50903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>151800</t>
+          <t>150988</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170242</t>
+          <t>170584</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>152134</t>
+          <t>151683</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168211</t>
+          <t>168167</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>310353</t>
+          <t>308769</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335066</t>
+          <t>334892</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25207</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38608</t>
+          <t>39337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>18725</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,62 +1673,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2861</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3503</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>161298</t>
+          <t>161297</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55772</t>
+          <t>48428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>397033</t>
+          <t>399157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70327</t>
+          <t>70164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76837</t>
+          <t>76758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90464</t>
+          <t>70519</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>471422</t>
+          <t>471461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>14310</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>359117</t>
+          <t>366397</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>403226</t>
+          <t>422816</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4193</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>412</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2512</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3196</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,62 +2242,62 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5966</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>419606</t>
+          <t>420383</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>440309</t>
+          <t>440472</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>302621</t>
+          <t>300774</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>318584</t>
+          <t>318658</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>728495</t>
+          <t>728369</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>754729</t>
+          <t>754388</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30745</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31500</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31578</t>
+          <t>31983</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57118</t>
+          <t>56119</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>203463</t>
+          <t>203546</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>217292</t>
+          <t>217446</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>372080</t>
+          <t>372231</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>397829</t>
+          <t>398782</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>582264</t>
+          <t>582209</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>609559</t>
+          <t>609452</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32002</t>
+          <t>32563</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44482</t>
+          <t>44192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,82 +3360,82 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>4941</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>10195</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>4941</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>9895</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>4941</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>1845</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>9853</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>4941</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>112331</t>
+          <t>113322</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>276877</t>
+          <t>277012</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>298262</t>
+          <t>298795</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>396323</t>
+          <t>396598</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>420383</t>
+          <t>420297</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35463</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38053</t>
+          <t>39811</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>756887</t>
+          <t>802494</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1527441</t>
+          <t>1530177</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1396810</t>
+          <t>1399457</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1441186</t>
+          <t>1443190</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2058644</t>
+          <t>2062820</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2947251</t>
+          <t>2950979</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>78089</t>
+          <t>76604</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>854927</t>
+          <t>811736</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>83713</t>
+          <t>84674</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>123133</t>
+          <t>121098</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>180552</t>
+          <t>176051</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1074518</t>
+          <t>1083555</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>21891</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>27854</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>17471</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39707</t>
+          <t>40104</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>838</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>22207</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D4_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D4_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>203047</t>
+          <t>222191</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>188692</t>
+          <t>207613</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>212019</t>
+          <t>231668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>198708</t>
+          <t>213671</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190066</t>
+          <t>204333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>204952</t>
+          <t>219818</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>401755</t>
+          <t>435862</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>386046</t>
+          <t>419118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>413660</t>
+          <t>447744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32972</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>20450</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27098</t>
+          <t>29443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35762</t>
+          <t>37870</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>26294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50903</t>
+          <t>53774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>703</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>162452</t>
+          <t>177318</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>150988</t>
+          <t>165346</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170584</t>
+          <t>185584</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>162347</t>
+          <t>179564</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>151683</t>
+          <t>169777</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168167</t>
+          <t>185393</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>324798</t>
+          <t>356882</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>308769</t>
+          <t>343141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>334892</t>
+          <t>367504</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27911</t>
+          <t>26974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39337</t>
+          <t>39556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>13208</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18725</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>161297</t>
+          <t>177718</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48428</t>
+          <t>168891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>399157</t>
+          <t>183132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>74455</t>
+          <t>81746</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70164</t>
+          <t>77524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76758</t>
+          <t>84258</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>235752</t>
+          <t>259463</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70519</t>
+          <t>250338</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>471461</t>
+          <t>265623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>252894</t>
+          <t>10125</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>366397</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>256979</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>422816</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>432</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,27 +2432,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>431979</t>
+          <t>484438</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>420383</t>
+          <t>469091</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>440472</t>
+          <t>494374</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>311042</t>
+          <t>353856</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>300774</t>
+          <t>344169</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>318658</t>
+          <t>362518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>743020</t>
+          <t>838294</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>728369</t>
+          <t>818521</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>754388</t>
+          <t>850698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>22526</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>36916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>34704</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>42385</t>
+          <t>48971</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31983</t>
+          <t>37651</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56119</t>
+          <t>68082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>758</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>11217</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>794765</t>
+          <t>898501</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>794765</t>
+          <t>898501</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>794765</t>
+          <t>898501</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>212037</t>
+          <t>255721</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>203546</t>
+          <t>247283</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>217446</t>
+          <t>261007</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>383505</t>
+          <t>353710</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>372231</t>
+          <t>343701</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>398782</t>
+          <t>361349</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>595542</t>
+          <t>609431</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>582209</t>
+          <t>596352</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>609452</t>
+          <t>619269</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18139</t>
+          <t>18226</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>17696</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>32524</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>32699</t>
+          <t>34095</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>25439</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44192</t>
+          <t>45396</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>528</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>637956</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>637956</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>637956</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,22 +3570,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>120514</t>
+          <t>114637</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113322</t>
+          <t>107911</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>289916</t>
+          <t>323005</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>277012</t>
+          <t>309899</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>298795</t>
+          <t>332114</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>410431</t>
+          <t>437642</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>396598</t>
+          <t>423539</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>420297</t>
+          <t>447909</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>25096</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35161</t>
+          <t>37372</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>25573</t>
+          <t>27896</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39811</t>
+          <t>42259</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,22 +3979,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>318122</t>
+          <t>354500</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>318122</t>
+          <t>354500</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>318122</t>
+          <t>354500</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>441450</t>
+          <t>471937</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>441450</t>
+          <t>471937</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>441450</t>
+          <t>471937</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1291325</t>
+          <t>1432023</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>802494</t>
+          <t>1408334</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1530177</t>
+          <t>1450118</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1419973</t>
+          <t>1505552</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1399457</t>
+          <t>1483306</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1443190</t>
+          <t>1524741</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2711299</t>
+          <t>2937574</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2062820</t>
+          <t>2907601</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2950979</t>
+          <t>2967519</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>316703</t>
+          <t>77772</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>76604</t>
+          <t>60526</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>811736</t>
+          <t>99674</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>102087</t>
+          <t>112757</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>84674</t>
+          <t>95847</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>121098</t>
+          <t>133052</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>418790</t>
+          <t>190529</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>176051</t>
+          <t>166133</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1083555</t>
+          <t>220692</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -4365,102 +4365,102 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>16890</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>10773</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>26149</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>29164</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>19913</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>42052</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
           <t>1,33%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>14859</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>9114</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>27854</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>26684</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>17471</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>40104</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16470</t>
+          <t>18677</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>22207</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1547675</t>
+          <t>1647114</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1547675</t>
+          <t>1647114</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1547675</t>
+          <t>1647114</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3170909</t>
+          <t>3172567</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3170909</t>
+          <t>3172567</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3170909</t>
+          <t>3172567</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
